--- a/output/pdf_financials_xlsx/AXE.xlsx
+++ b/output/pdf_financials_xlsx/AXE.xlsx
@@ -5398,28 +5398,28 @@
         <v>6.180534</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>6.868369</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>7.35002</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>7.440067</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>7.856632</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>8.620070999999999</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>9.108283</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>9.675565000000001</v>
       </c>
       <c r="P92" s="3" t="n">
         <v>0</v>
@@ -10662,7 +10662,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -13456,7 +13460,11 @@
           <t>Reserves (note 11)</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AXE.xlsx
+++ b/output/pdf_financials_xlsx/AXE.xlsx
@@ -938,13 +938,13 @@
         </is>
       </c>
       <c r="M10" s="3" t="n">
-        <v>3.445155</v>
+        <v>5.542099</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.25474</v>
+        <v>2.24854</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>1.025582</v>
+        <v>2.657687</v>
       </c>
       <c r="P10" s="1" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">

--- a/output/pdf_financials_xlsx/AXE.xlsx
+++ b/output/pdf_financials_xlsx/AXE.xlsx
@@ -6381,13 +6381,13 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.00252</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.008233000000000001</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.048876</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -6402,7 +6402,7 @@
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.005489</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
@@ -6423,7 +6423,7 @@
         <v>0</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>0.232458</v>
       </c>
     </row>
     <row r="113">
@@ -6823,13 +6823,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>0</v>
+        <v>2.012468</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>0</v>
+        <v>0.944392</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>0</v>
+        <v>1.121953</v>
       </c>
       <c r="K120" s="3" t="n">
         <v>0</v>
@@ -18814,7 +18814,11 @@
           <t>Proceeds from sale of property and equipment (note 16)</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -24950,7 +24954,11 @@
           <t>Issuance of common shares, net of issue costs (note 11a)</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -25203,7 +25211,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -28362,7 +28374,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E235" s="5" t="n">
         <v>0.00252</v>
       </c>

--- a/output/pdf_financials_xlsx/AXE.xlsx
+++ b/output/pdf_financials_xlsx/AXE.xlsx
@@ -1310,7 +1310,7 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.917196</v>
+        <v>-0.917196</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -3898,10 +3898,10 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.036265</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.027663</v>
       </c>
       <c r="F64" s="3" t="n">
         <v>0</v>
@@ -4051,31 +4051,31 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.075447</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.181797</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.130646</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.09159299999999999</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.083912</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.051122</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.059224</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.673168</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.825466</v>
       </c>
       <c r="L67" s="3" t="n">
         <v>0</v>
@@ -4087,10 +4087,10 @@
         <v>0</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>1.547094</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>1.697828</v>
       </c>
     </row>
     <row r="68">
@@ -6148,22 +6148,22 @@
         <v>0.624359</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>0.477505</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>0.218831</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>0.276686</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>0.5706329999999999</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>0.539428</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>0.200447</v>
       </c>
     </row>
     <row r="108">
@@ -17527,7 +17527,11 @@
           <t>Share-based payments expense (note 11(c))</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -21594,7 +21598,11 @@
           <t>Share-based payments expense (note 10(c))</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -22842,7 +22850,11 @@
           <t>Share-based payments expense (note 11(b))</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -44610,7 +44622,11 @@
           <t>Deferred income tax recovery (note 15)</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
